--- a/artfynd/A 17577-2026 artfynd.xlsx
+++ b/artfynd/A 17577-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104729191</v>
+        <v>129418242</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>5685</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Frostbo- området mot Dragmossen, Upl</t>
+          <t>Östanå O ca 2,5 km, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637619.1764284006</v>
+        <v>637988</v>
       </c>
       <c r="R2" t="n">
-        <v>6716132.02643191</v>
+        <v>6716548</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Bergvik skog öst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +762,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>ung sumpskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -799,12 +790,7 @@
         <v>104766041</v>
       </c>
       <c r="B3" t="n">
-        <v>42702</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638045.5038166658</v>
+        <v>638046</v>
       </c>
       <c r="R3" t="n">
-        <v>6716317.174594086</v>
+        <v>6716317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +869,9 @@
           <t>2022-08-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +901,7 @@
         <v>129418243</v>
       </c>
       <c r="B4" t="n">
-        <v>98697</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,6 +1002,112 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104729191</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Frostbo- området mot Dragmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>637619</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6716132</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17577-2026 artfynd.xlsx
+++ b/artfynd/A 17577-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129418242</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104766041</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129418243</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,8 +1128,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104729191</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>